--- a/tests/fixtures/corpus/pivot.xlsx
+++ b/tests/fixtures/corpus/pivot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DC56E1A-979A-47BE-B77C-D21A308C4C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2176BE13-0033-4E98-8D95-4062245DA4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="16200" windowHeight="9307" xr2:uid="{99CE2C5C-C480-421B-98D8-7E85DF9E1754}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="16200" windowHeight="9307" xr2:uid="{46D31B7B-9B05-41CE-A43D-355BFBE11ABC}"/>
   </bookViews>
   <sheets>
     <sheet name="Pvt" sheetId="2" r:id="rId1"/>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Zeta" refreshedDate="46268.216115856485" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{93E7622F-A0C9-49AB-A3D0-6811DBF30EB3}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Zeta" refreshedDate="46269.75837476852" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{C5FA8C8B-A9DF-4D8C-BF9C-39E31C1D46A9}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:C7" sheet="Src"/>
   </cacheSource>
@@ -195,7 +195,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7280459E-8025-4848-ABF1-4A81ADE89A92}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{54654032-7318-4F58-8AA9-362C3C4D1F07}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -556,7 +556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C54278-2C15-4DD4-9C60-4A141830E899}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661E1F00-5C21-433B-9AC6-F94FA5009536}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -602,7 +602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5748E3-FE9D-46CA-96AE-6B47D3F55808}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C19F5B3-BC26-48D4-93C7-3561D5EA7495}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
